--- a/docs/coze/coze_2026-03-07.xlsx
+++ b/docs/coze/coze_2026-03-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>时间</t>
   </si>
@@ -47,6 +47,60 @@
   </si>
   <si>
     <t>[{"direction":"LONG","probability":30,"setup_logic":"Bullish Order Block at 68121.6-68367.6","trigger_condition":"Break above 68759.5","entry_price":68760,"stop_loss":68120,"take_profit_1":69000,"take_profit_2":69200,"risk_reward_ratio":2,"action":"WAIT"},{"direction":"SHORT","probability":40,"setup_logic":"Bearish Liquidity Grab at 69054-69179.4","trigger_condition":"Break below 68413.8","entry_price":68410,"stop_loss":69050,"take_profit_1":68000,"take_profit_2":67500,"risk_reward_ratio":1.8,"action":"WAIT"},{"direction":"SIDEWAYS","probability":30,"setup_logic":"Consolidation between 68121.6-69079.6","trigger_condition":"No breakout above/below 68759.5/68413.8","entry_price":null,"stop_loss":null,"take_profit_1":null,"take_profit_2":null,"risk_reward_ratio":null,"action":"SKIP"}]</t>
+  </si>
+  <si>
+    <t>2026-03-07 01:44:58</t>
+  </si>
+  <si>
+    <t>2026-03-07T01:44:50Z</t>
+  </si>
+  <si>
+    <t>Bearish Liquidity Sweep (LL/LH Breakdown)</t>
+  </si>
+  <si>
+    <t>[{"direction":"LONG","probability":25,"setup_logic":"Bullish Order Block at 68160-68360","trigger_condition":"Break above 68555 with volume confirmation","entry_price":68555.2,"stop_loss":68160.6,"take_profit_1":68900,"take_profit_2":69250,"risk_reward_ratio":1.6,"action":"WAIT"},{"direction":"SHORT","probability":55,"setup_logic":"Bearish Liquidity Grab at 68555-68759","trigger_condition":"Break below 68303.6 with volume confirmation","entry_price":68303.6,"stop_loss":68759.5,"take_profit_1":67950,"take_profit_2":67600,"risk_reward_ratio":1.7,"action":"WAIT"},{"direction":"SIDEWAYS","probability":20,"setup_logic":"Consolidation between 68160-68555","trigger_condition":"No breakout above/below key levels within 5 candles","entry_price":null,"stop_loss":null,"take_profit_1":null,"take_profit_2":null,"risk_reward_ratio":null,"action":"SKIP"}]</t>
+  </si>
+  <si>
+    <t>2026-03-07 01:46:56</t>
+  </si>
+  <si>
+    <t>2026-03-07T01:46:50Z</t>
+  </si>
+  <si>
+    <t>Liquidity Sweep (LL/LH)</t>
+  </si>
+  <si>
+    <t>[{"direction":"LONG","probability":30,"setup_logic":"Bullish Order Block at 68258.8-68303.6","trigger_condition":"Break above 68555.2","entry_price":68555.2,"stop_loss":68160.6,"take_profit_1":68900,"take_profit_2":69250,"risk_reward_ratio":1.65,"action":"WAIT"},{"direction":"SHORT","probability":40,"setup_logic":"Bearish Liquidity Grab at 69179.4-69241.1","trigger_condition":"Break below 68221.1","entry_price":68221.1,"stop_loss":68553.9,"take_profit_1":67800,"take_profit_2":67450,"risk_reward_ratio":1.75,"action":"WAIT"},{"direction":"SIDEWAYS","probability":30,"setup_logic":"Range 67712.3-68986.9","trigger_condition":"No breakout above/below","entry_price":null,"stop_loss":null,"take_profit_1":null,"take_profit_2":null,"risk_reward_ratio":null,"action":"SKIP"}]</t>
+  </si>
+  <si>
+    <t>2026-03-07 02:21:34</t>
+  </si>
+  <si>
+    <t>2026-03-06T15:05:00Z</t>
+  </si>
+  <si>
+    <t>[{"direction":"LONG","probability":30,"setup_logic":"Bullish Order Block at 67712.3","trigger_condition":"Break above 68368.8","entry_price":68370,"stop_loss":67712.3,"take_profit_1":68555.2,"take_profit_2":68707.2,"risk_reward_ratio":1.85,"action":"WAIT"},{"direction":"SHORT","probability":40,"setup_logic":"Bearish Liquidity Zone at 68677.4","trigger_condition":"Break below 68160.6","entry_price":68160.6,"stop_loss":68677.4,"take_profit_1":67712.3,"take_profit_2":67300,"risk_reward_ratio":1.95,"action":"WAIT"},{"direction":"SIDEWAYS","probability":30,"setup_logic":"Consolidation Range 68160.6-68677.4","trigger_condition":"No breakout above/below","entry_price":null,"stop_loss":null,"take_profit_1":null,"take_profit_2":null,"risk_reward_ratio":null,"action":"SKIP"}]</t>
+  </si>
+  <si>
+    <t>2026-03-07 02:55:06</t>
+  </si>
+  <si>
+    <t>2026-03-07T02:55:02Z</t>
+  </si>
+  <si>
+    <t>[{"direction":"LONG","probability":30,"setup_logic":"Bullish Order Block at 67712-67809","trigger_condition":"Break above 68300 with volume confirmation","entry_price":68300,"stop_loss":67712.3,"take_profit_1":68800,"take_profit_2":69200,"risk_reward_ratio":1.8,"action":"WAIT"},{"direction":"SHORT","probability":40,"setup_logic":"Bearish Liquidity Rejection at 68468","trigger_condition":"Break below 68186 with volume spike","entry_price":68186,"stop_loss":68642.4,"take_profit_1":67700,"take_profit_2":67200,"risk_reward_ratio":1.9,"action":"WAIT"},{"direction":"SIDEWAYS","probability":30,"setup_logic":"Consolidation between 67712-68555","trigger_condition":"No breakouts above/below key levels","entry_price":null,"stop_loss":null,"take_profit_1":null,"take_profit_2":null,"risk_reward_ratio":null,"action":"SKIP"}]</t>
+  </si>
+  <si>
+    <t>2026-03-07 03:14:54</t>
+  </si>
+  <si>
+    <t>2026-03-07T03:14:48Z</t>
+  </si>
+  <si>
+    <t>Bearish Liquidity Grab at 67712</t>
+  </si>
+  <si>
+    <t>[{"direction":"LONG","probability":30,"setup_logic":"Bullish Order Block at 68160-68221","trigger_condition":"Break above 68460","entry_price":68460,"stop_loss":68087,"take_profit_1":68750,"take_profit_2":69000,"risk_reward_ratio":1.5,"action":"WAIT"},{"direction":"SHORT","probability":40,"setup_logic":"Bearish Order Block at 68402-68444","trigger_condition":"Break below 68144","entry_price":68144,"stop_loss":68439.8,"take_profit_1":67900,"take_profit_2":67700,"risk_reward_ratio":1.6,"action":"WAIT"},{"direction":"SIDEWAYS","probability":30,"setup_logic":"Consolidation from 68144-68460","trigger_condition":"No breakout via 68460/68144","entry_price":null,"stop_loss":null,"take_profit_1":null,"take_profit_2":null,"risk_reward_ratio":null,"action":"SKIP"}]</t>
   </si>
 </sst>
 </file>
@@ -393,6 +447,106 @@
         <v>10</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>67780.3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>67857.4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>68286</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>68201</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>68370</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/docs/coze/coze_2026-03-07.xlsx
+++ b/docs/coze/coze_2026-03-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>时间</t>
   </si>
@@ -101,6 +101,69 @@
   </si>
   <si>
     <t>[{"direction":"LONG","probability":30,"setup_logic":"Bullish Order Block at 68160-68221","trigger_condition":"Break above 68460","entry_price":68460,"stop_loss":68087,"take_profit_1":68750,"take_profit_2":69000,"risk_reward_ratio":1.5,"action":"WAIT"},{"direction":"SHORT","probability":40,"setup_logic":"Bearish Order Block at 68402-68444","trigger_condition":"Break below 68144","entry_price":68144,"stop_loss":68439.8,"take_profit_1":67900,"take_profit_2":67700,"risk_reward_ratio":1.6,"action":"WAIT"},{"direction":"SIDEWAYS","probability":30,"setup_logic":"Consolidation from 68144-68460","trigger_condition":"No breakout via 68460/68144","entry_price":null,"stop_loss":null,"take_profit_1":null,"take_profit_2":null,"risk_reward_ratio":null,"action":"SKIP"}]</t>
+  </si>
+  <si>
+    <t>2026-03-07 03:15:54</t>
+  </si>
+  <si>
+    <t>2026-03-07T03:15:48Z</t>
+  </si>
+  <si>
+    <t>Bearish Sweep at 68593.9</t>
+  </si>
+  <si>
+    <t>[{"direction":"LONG","probability":30,"setup_logic":"Bullish Order Block Rejection at 67712.3","trigger_condition":"Break above 68444.0","entry_price":68450,"stop_loss":67712.3,"take_profit_1":68644,"take_profit_2":68838,"risk_reward_ratio":2,"action":"WAIT"},{"direction":"SHORT","probability":45,"setup_logic":"Bearish Liquidity Grab at 68593.9","trigger_condition":"Break below 68160.6","entry_price":68150,"stop_loss":68593.9,"take_profit_1":67900,"take_profit_2":67650,"risk_reward_ratio":2,"action":"WAIT"},{"direction":"SIDEWAYS","probability":25,"setup_logic":"Consolidation Range 67712.3-68593.9","trigger_condition":"No breakout above/below range","entry_price":null,"stop_loss":null,"take_profit_1":null,"take_profit_2":null,"risk_reward_ratio":null,"action":"SKIP"}]</t>
+  </si>
+  <si>
+    <t>2026-03-07 03:16:54</t>
+  </si>
+  <si>
+    <t>2026-03-07T03:16:47Z</t>
+  </si>
+  <si>
+    <t>未指定</t>
+  </si>
+  <si>
+    <t>[{"direction":"LONG","probability":30,"setup_logic":"Bullish Order Block at 67712.3-67809.6","trigger_condition":"Break above 68444.0","entry_price":68445,"stop_loss":67712.3,"take_profit_1":68759.5,"take_profit_2":69054,"risk_reward_ratio":2.1,"action":"WAIT"},{"direction":"SHORT","probability":45,"setup_logic":"Bearish Liquidity Grab at 68444.0","trigger_condition":"Break below 67712.3","entry_price":67712.3,"stop_loss":68444,"take_profit_1":67300,"take_profit_2":67000,"risk_reward_ratio":1.8,"action":"SKIP"},{"direction":"SIDEWAYS","probability":25,"setup_logic":"Consolidation between 67712.3-68444.0","trigger_condition":"No breakout above/below","entry_price":null,"stop_loss":null,"take_profit_1":null,"take_profit_2":null,"risk_reward_ratio":null,"action":"SKIP"}]</t>
+  </si>
+  <si>
+    <t>2026-03-07 03:17:54</t>
+  </si>
+  <si>
+    <t>2026-03-07T03:17:47Z</t>
+  </si>
+  <si>
+    <t>[{"direction":"LONG","probability":30,"setup_logic":"Bullish Order Block at 67712.3-67809.6","trigger_condition":"Break above 68444.0 with volume confirmation","entry_price":68450,"stop_loss":67700,"take_profit_1":68700,"take_profit_2":68950,"risk_reward_ratio":1.9,"action":"WAIT"},{"direction":"SHORT","probability":40,"setup_logic":"Bearish Liquidity Rejection at 68444.0","trigger_condition":"Break below 68144.0 with volume spike","entry_price":68130,"stop_loss":68450,"take_profit_1":67900,"take_profit_2":67650,"risk_reward_ratio":1.8,"action":"SKIP"},{"direction":"SIDEWAYS","probability":30,"setup_logic":"Consolidation between 67712.3-68444.0","trigger_condition":"No breakout above/below key levels","entry_price":null,"stop_loss":null,"take_profit_1":null,"take_profit_2":null,"risk_reward_ratio":null,"action":"SKIP"}]</t>
+  </si>
+  <si>
+    <t>2026-03-07 03:19:12</t>
+  </si>
+  <si>
+    <t>2026-03-07T03:19:06Z</t>
+  </si>
+  <si>
+    <t>Bearish Liquidity Sweep (LL/LH)</t>
+  </si>
+  <si>
+    <t>[{"direction":"LONG","probability":35,"setup_logic":"Bullish Order Block at 67712.3-67809.6","trigger_condition":"Break above 68444.0 with volume confirmation","entry_price":68450,"stop_loss":67700,"take_profit_1":68700,"take_profit_2":68950,"risk_reward_ratio":2.1,"action":"WAIT"},{"direction":"SHORT","probability":45,"setup_logic":"Bearish Market Structure Breakdown (HH/HL)","trigger_condition":"Close below 68144.0 with volume spike","entry_price":68140,"stop_loss":68450,"take_profit_1":67800,"take_profit_2":67500,"risk_reward_ratio":1.8,"action":"WAIT"},{"direction":"SIDEWAYS","probability":20,"setup_logic":"Consolidation between 67712.3-68444.0","trigger_condition":"Price action within 68000-68500 range","entry_price":null,"stop_loss":null,"take_profit_1":null,"take_profit_2":null,"risk_reward_ratio":null,"action":"SKIP"}]</t>
+  </si>
+  <si>
+    <t>2026-03-07 03:20:15</t>
+  </si>
+  <si>
+    <t>2026-03-07T03:20:09Z</t>
+  </si>
+  <si>
+    <t>[{"direction":"LONG","probability":25,"setup_logic":"Liquidity Bounce from 67712.3","trigger_condition":"Break above 68412.0","entry_price":68415,"stop_loss":67712.3,"take_profit_1":68700,"take_profit_2":69000,"risk_reward_ratio":2,"action":"WAIT"},{"direction":"SHORT","probability":55,"setup_logic":"Bearish Momentum after 68700 Resistance","trigger_condition":"Break below 68087.0","entry_price":68050,"stop_loss":68412,"take_profit_1":67700,"take_profit_2":67300,"risk_reward_ratio":2,"action":"EXECUTE"},{"direction":"SIDEWAYS","probability":20,"setup_logic":"Consolidation 68100-68450","trigger_condition":"No breakout in next 5 candles","entry_price":null,"stop_loss":null,"take_profit_1":null,"take_profit_2":null,"risk_reward_ratio":null,"action":"SKIP"}]</t>
+  </si>
+  <si>
+    <t>2026-03-07 03:21:08</t>
+  </si>
+  <si>
+    <t>2026-03-07T03:21:02Z</t>
+  </si>
+  <si>
+    <t>[{"direction":"LONG","probability":35,"setup_logic":"Bullish Order Block at 67712.3-67809.6","trigger_condition":"Break above 68468.4","entry_price":68470,"stop_loss":67710,"take_profit_1":68800,"take_profit_2":69100,"risk_reward_ratio":2.1,"action":"WAIT"},{"direction":"SHORT","probability":45,"setup_logic":"Bearish Liquidity Grab at 68593.9-68611.4","trigger_condition":"Break below 68160.6","entry_price":68150,"stop_loss":68590,"take_profit_1":67800,"take_profit_2":67500,"risk_reward_ratio":1.8,"action":"EXECUTE"},{"direction":"SIDEWAYS","probability":20,"setup_logic":"Consolidation between 68160.6-68593.9","trigger_condition":"No breakout above 68593.9 or below 68160.6","entry_price":null,"stop_loss":null,"take_profit_1":null,"take_profit_2":null,"risk_reward_ratio":null,"action":"SKIP"}]</t>
   </si>
 </sst>
 </file>
@@ -547,6 +610,126 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>68379</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9">
+        <v>68418</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>68417.9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>68329.2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <v>68408.1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>68370.8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>